--- a/data/Mörel-Filet/cost/total_demand.xlsx
+++ b/data/Mörel-Filet/cost/total_demand.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49946.00836022617</v>
+        <v>2081.08368167609</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25214.3926698888</v>
+        <v>1050.5996945787</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>193158.8669477699</v>
+        <v>8048.286122823747</v>
       </c>
     </row>
   </sheetData>
